--- a/data/trans_orig/P79A7_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79A7_2023-Clase-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>695</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>695</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>695</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2853,27 +2853,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>19424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>19424</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>19424</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>19424</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
